--- a/guides/planilha_fluxo_de_caixa.xlsx
+++ b/guides/planilha_fluxo_de_caixa.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lancamentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DRE Simplificado" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Contas a Pagar-Receber" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lancamentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE Simplificado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas a Pagar-Receber" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suporte" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +37,16 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E4A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,9 +74,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -143,13 +156,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -172,14 +185,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -204,14 +217,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -263,13 +276,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -292,7 +305,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -320,7 +333,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -335,9 +348,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -357,9 +370,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1049,7 +1062,6 @@
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1083,7 +1095,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1115,7 +1126,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -1176,4 +1186,45 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Duvidas ou sugestoes?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Siga a Skill Hub no Instagram:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>@skillhub.tec</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>